--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Paleswarankandigai_13.405539_80.123205.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Paleswarankandigai_13.405539_80.123205.xlsx
@@ -698,6 +698,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
